--- a/香港現在上映電影 2026-01-29.xlsx
+++ b/香港現在上映電影 2026-01-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="141">
   <si>
     <t>英文名稱</t>
   </si>
@@ -44,13 +44,406 @@
   </si>
   <si>
     <t>全球票房</t>
+  </si>
+  <si>
+    <t>國寶</t>
+  </si>
+  <si>
+    <t>純屬伊朗意外</t>
+  </si>
+  <si>
+    <t>鏈鋸人 - 劇場版：蕾潔篇</t>
+  </si>
+  <si>
+    <t>一戰再戰</t>
+  </si>
+  <si>
+    <t>28 年後：人骨聖殿</t>
+  </si>
+  <si>
+    <t>優獸大都會2</t>
+  </si>
+  <si>
+    <t>腦細天劫</t>
+  </si>
+  <si>
+    <t>魔法壞女巫 : 第二章</t>
+  </si>
+  <si>
+    <t>怪奇魔塵事件</t>
+  </si>
+  <si>
+    <t>猩瘋血雨</t>
+  </si>
+  <si>
+    <t>悠唱藍調</t>
+  </si>
+  <si>
+    <t>末世綠洲</t>
+  </si>
+  <si>
+    <t>換乘真愛</t>
+  </si>
+  <si>
+    <t>美傭誘罪</t>
+  </si>
+  <si>
+    <t>紐倫堡</t>
+  </si>
+  <si>
+    <t>阿凡達 3</t>
+  </si>
+  <si>
+    <t>天劫倒數：大遷徙</t>
+  </si>
+  <si>
+    <t>狂蟒之災</t>
+  </si>
+  <si>
+    <t>讓悲傷長出翅膀</t>
+  </si>
+  <si>
+    <t>法無赦</t>
+  </si>
+  <si>
+    <t>Kokuho</t>
+  </si>
+  <si>
+    <t>It Was Just an Accident</t>
+  </si>
+  <si>
+    <t>Chainsaw Man: The Movie: Reze Arc</t>
+  </si>
+  <si>
+    <t>One Battle After Another</t>
+  </si>
+  <si>
+    <t>28 Years Later: The Bone Temple</t>
+  </si>
+  <si>
+    <t>Zootopia 2</t>
+  </si>
+  <si>
+    <t>Send Help</t>
+  </si>
+  <si>
+    <t>Wicked: For Good</t>
+  </si>
+  <si>
+    <t>Dust Bunny</t>
+  </si>
+  <si>
+    <t>PRIMATE</t>
+  </si>
+  <si>
+    <t>Song Sung Blue</t>
+  </si>
+  <si>
+    <t>Greenland</t>
+  </si>
+  <si>
+    <t>Eternity</t>
+  </si>
+  <si>
+    <t>The Housemaid</t>
+  </si>
+  <si>
+    <t>Nuremberg</t>
+  </si>
+  <si>
+    <t>Avatar: Fire and Ash</t>
+  </si>
+  <si>
+    <t>Greenland 2: Migration</t>
+  </si>
+  <si>
+    <t>Anaconda</t>
+  </si>
+  <si>
+    <t>The Thing with Feathers</t>
+  </si>
+  <si>
+    <t>Mercy</t>
+  </si>
+  <si>
+    <t>12/11/2025</t>
+  </si>
+  <si>
+    <t>15/10/2025</t>
+  </si>
+  <si>
+    <t>24/9/2025</t>
+  </si>
+  <si>
+    <t>14/1/2026</t>
+  </si>
+  <si>
+    <t>26/11/2025</t>
+  </si>
+  <si>
+    <t>28/1/2026</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>21/1/2026</t>
+  </si>
+  <si>
+    <t>24/9/2020</t>
+  </si>
+  <si>
+    <t>18/12/2025</t>
+  </si>
+  <si>
+    <t>24/12/2025</t>
+  </si>
+  <si>
+    <t>7/1/2026</t>
+  </si>
+  <si>
+    <t>23/12/2025</t>
+  </si>
+  <si>
+    <t>31/12/2025</t>
+  </si>
+  <si>
+    <t>劇情</t>
+  </si>
+  <si>
+    <t>劇情、驚悚</t>
+  </si>
+  <si>
+    <t>動作、冒險、奇幻、動漫</t>
+  </si>
+  <si>
+    <t>驚悚、喜劇</t>
+  </si>
+  <si>
+    <t>恐怖、驚悚</t>
+  </si>
+  <si>
+    <t>親子、喜劇、冒險、動畫</t>
+  </si>
+  <si>
+    <t>親子、音樂劇、奇幻、冒險</t>
+  </si>
+  <si>
+    <t>奇幻、恐怖</t>
+  </si>
+  <si>
+    <t>劇情、音樂</t>
+  </si>
+  <si>
+    <t>動作、冒險、驚悚</t>
+  </si>
+  <si>
+    <t>浪漫、喜劇、劇情、奇幻</t>
+  </si>
+  <si>
+    <t>驚悚、劇情</t>
+  </si>
+  <si>
+    <t>歷史、劇情</t>
+  </si>
+  <si>
+    <t>科幻、冒險、動作、奇幻</t>
+  </si>
+  <si>
+    <t>喜劇、冒險、恐怖</t>
+  </si>
+  <si>
+    <t>科幻、動作、驚悚、劇情</t>
+  </si>
+  <si>
+    <t>2h 54m</t>
+  </si>
+  <si>
+    <t>1h 45m</t>
+  </si>
+  <si>
+    <t>1h 40m</t>
+  </si>
+  <si>
+    <t>2h 41m</t>
+  </si>
+  <si>
+    <t>1h 50m</t>
+  </si>
+  <si>
+    <t>1h 48m</t>
+  </si>
+  <si>
+    <t>1h 53m</t>
+  </si>
+  <si>
+    <t>2h 40m</t>
+  </si>
+  <si>
+    <t>1h 46m</t>
+  </si>
+  <si>
+    <t>1h 29m</t>
+  </si>
+  <si>
+    <t>2h 12m</t>
+  </si>
+  <si>
+    <t>1h 59m</t>
+  </si>
+  <si>
+    <t>1h 54m</t>
+  </si>
+  <si>
+    <t>2h 11m</t>
+  </si>
+  <si>
+    <t>2h 28m</t>
+  </si>
+  <si>
+    <t>3h 12m</t>
+  </si>
+  <si>
+    <t>1h 38m</t>
+  </si>
+  <si>
+    <t>1h 39m</t>
+  </si>
+  <si>
+    <t>1h 44m</t>
+  </si>
+  <si>
+    <t>IIA</t>
+  </si>
+  <si>
+    <t>IIB</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>9.789億</t>
+  </si>
+  <si>
+    <t>7800萬</t>
+  </si>
+  <si>
+    <t>13.59億</t>
+  </si>
+  <si>
+    <t>16.15億</t>
+  </si>
+  <si>
+    <t>3.666億</t>
+  </si>
+  <si>
+    <t>136.2億</t>
+  </si>
+  <si>
+    <t>59.19億</t>
+  </si>
+  <si>
+    <t>780萬</t>
+  </si>
+  <si>
+    <t>2.418億</t>
+  </si>
+  <si>
+    <t>4.134億</t>
+  </si>
+  <si>
+    <t>4.079億</t>
+  </si>
+  <si>
+    <t>2.964億</t>
+  </si>
+  <si>
+    <t>23.82億</t>
+  </si>
+  <si>
+    <t>3.354億</t>
+  </si>
+  <si>
+    <t>107.6億</t>
+  </si>
+  <si>
+    <t>1.794億</t>
+  </si>
+  <si>
+    <t>10.06億</t>
+  </si>
+  <si>
+    <t>470.2萬</t>
+  </si>
+  <si>
+    <t>1.950億</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +460,20 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="CALIBRI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="CALIBRI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF0000FF"/>
       <name val="CALIBRI"/>
       <family val="2"/>
     </font>
@@ -91,12 +498,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -393,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41.7109375" style="1" customWidth="1"/>
@@ -409,7 +822,7 @@
     <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11">
+    <row r="1" spans="1:11">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -441,7 +854,782 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="1">
+        <v>22</v>
+      </c>
+      <c r="H2" s="1">
+        <v>96</v>
+      </c>
+      <c r="I2" s="1">
+        <v>50</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1">
+        <v>199</v>
+      </c>
+      <c r="H3" s="1">
+        <v>92</v>
+      </c>
+      <c r="I3" s="1">
+        <v>50</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46</v>
+      </c>
+      <c r="H4" s="1">
+        <v>98</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="1">
+        <v>434</v>
+      </c>
+      <c r="H5" s="1">
+        <v>85</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="1">
+        <v>298</v>
+      </c>
+      <c r="H6" s="1">
+        <v>88</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="1">
+        <v>219</v>
+      </c>
+      <c r="H7" s="1">
+        <v>96</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="1">
+        <v>93</v>
+      </c>
+      <c r="I8" s="1">
+        <v>50</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G9" s="1">
+        <v>407</v>
+      </c>
+      <c r="H9" s="1">
+        <v>95</v>
+      </c>
+      <c r="I9" s="1">
+        <v>25000</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="1">
+        <v>107</v>
+      </c>
+      <c r="H10" s="1">
+        <v>81</v>
+      </c>
+      <c r="I10" s="1">
+        <v>100</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="1">
+        <v>160</v>
+      </c>
+      <c r="H11" s="1">
+        <v>71</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="1">
+        <v>196</v>
+      </c>
+      <c r="H12" s="1">
+        <v>97</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2500</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="1">
+        <v>160</v>
+      </c>
+      <c r="H13" s="1">
+        <v>63</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2500</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="1">
+        <v>186</v>
+      </c>
+      <c r="H14" s="1">
+        <v>90</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="1">
+        <v>193</v>
+      </c>
+      <c r="H15" s="1">
+        <v>92</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G16" s="1">
+        <v>190</v>
+      </c>
+      <c r="H16" s="1">
+        <v>95</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="1">
+        <v>344</v>
+      </c>
+      <c r="H17" s="1">
+        <v>90</v>
+      </c>
+      <c r="I17" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="1">
+        <v>85</v>
+      </c>
+      <c r="H18" s="1">
+        <v>66</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="1">
+        <v>152</v>
+      </c>
+      <c r="H19" s="1">
+        <v>76</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="1">
+        <v>71</v>
+      </c>
+      <c r="H20" s="1">
+        <v>55</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G21" s="1">
+        <v>151</v>
+      </c>
+      <c r="H21" s="1">
+        <v>82</v>
+      </c>
+      <c r="I21" s="1">
+        <v>500</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId2"/>
+    <hyperlink ref="F2" r:id="rId3"/>
+    <hyperlink ref="K2" r:id="rId4"/>
+    <hyperlink ref="A3" r:id="rId5"/>
+    <hyperlink ref="B3" r:id="rId6"/>
+    <hyperlink ref="F3" r:id="rId7"/>
+    <hyperlink ref="K3" r:id="rId8"/>
+    <hyperlink ref="A4" r:id="rId9"/>
+    <hyperlink ref="B4" r:id="rId10"/>
+    <hyperlink ref="F4" r:id="rId11"/>
+    <hyperlink ref="K4" r:id="rId12"/>
+    <hyperlink ref="A5" r:id="rId13"/>
+    <hyperlink ref="B5" r:id="rId14"/>
+    <hyperlink ref="F5" r:id="rId15"/>
+    <hyperlink ref="K5" r:id="rId16"/>
+    <hyperlink ref="A6" r:id="rId17"/>
+    <hyperlink ref="B6" r:id="rId18"/>
+    <hyperlink ref="F6" r:id="rId19"/>
+    <hyperlink ref="K6" r:id="rId20"/>
+    <hyperlink ref="A7" r:id="rId21"/>
+    <hyperlink ref="B7" r:id="rId22"/>
+    <hyperlink ref="F7" r:id="rId23"/>
+    <hyperlink ref="K7" r:id="rId24"/>
+    <hyperlink ref="A8" r:id="rId25"/>
+    <hyperlink ref="B8" r:id="rId26"/>
+    <hyperlink ref="F8" r:id="rId27"/>
+    <hyperlink ref="A9" r:id="rId28"/>
+    <hyperlink ref="B9" r:id="rId29"/>
+    <hyperlink ref="F9" r:id="rId30"/>
+    <hyperlink ref="K9" r:id="rId31"/>
+    <hyperlink ref="A10" r:id="rId32"/>
+    <hyperlink ref="B10" r:id="rId33"/>
+    <hyperlink ref="F10" r:id="rId34"/>
+    <hyperlink ref="K10" r:id="rId35"/>
+    <hyperlink ref="A11" r:id="rId36"/>
+    <hyperlink ref="B11" r:id="rId37"/>
+    <hyperlink ref="F11" r:id="rId38"/>
+    <hyperlink ref="K11" r:id="rId39"/>
+    <hyperlink ref="A12" r:id="rId40"/>
+    <hyperlink ref="B12" r:id="rId41"/>
+    <hyperlink ref="F12" r:id="rId42"/>
+    <hyperlink ref="K12" r:id="rId43"/>
+    <hyperlink ref="A13" r:id="rId44"/>
+    <hyperlink ref="B13" r:id="rId45"/>
+    <hyperlink ref="F13" r:id="rId46"/>
+    <hyperlink ref="K13" r:id="rId47"/>
+    <hyperlink ref="A14" r:id="rId48"/>
+    <hyperlink ref="B14" r:id="rId49"/>
+    <hyperlink ref="F14" r:id="rId50"/>
+    <hyperlink ref="K14" r:id="rId51"/>
+    <hyperlink ref="A15" r:id="rId52"/>
+    <hyperlink ref="B15" r:id="rId53"/>
+    <hyperlink ref="F15" r:id="rId54"/>
+    <hyperlink ref="K15" r:id="rId55"/>
+    <hyperlink ref="A16" r:id="rId56"/>
+    <hyperlink ref="B16" r:id="rId57"/>
+    <hyperlink ref="F16" r:id="rId58"/>
+    <hyperlink ref="K16" r:id="rId59"/>
+    <hyperlink ref="A17" r:id="rId60"/>
+    <hyperlink ref="B17" r:id="rId61"/>
+    <hyperlink ref="F17" r:id="rId62"/>
+    <hyperlink ref="K17" r:id="rId63"/>
+    <hyperlink ref="A18" r:id="rId64"/>
+    <hyperlink ref="B18" r:id="rId65"/>
+    <hyperlink ref="F18" r:id="rId66"/>
+    <hyperlink ref="K18" r:id="rId67"/>
+    <hyperlink ref="A19" r:id="rId68"/>
+    <hyperlink ref="B19" r:id="rId69"/>
+    <hyperlink ref="F19" r:id="rId70"/>
+    <hyperlink ref="K19" r:id="rId71"/>
+    <hyperlink ref="A20" r:id="rId72"/>
+    <hyperlink ref="B20" r:id="rId73"/>
+    <hyperlink ref="F20" r:id="rId74"/>
+    <hyperlink ref="K20" r:id="rId75"/>
+    <hyperlink ref="A21" r:id="rId76"/>
+    <hyperlink ref="B21" r:id="rId77"/>
+    <hyperlink ref="F21" r:id="rId78"/>
+    <hyperlink ref="K21" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>